--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486463_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486463_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6799</v>
+        <v>7.7531</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1603</v>
+        <v>2.8192</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5196</v>
+        <v>4.9339</v>
       </c>
       <c r="G2" t="n">
         <v>2.8569</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4081</v>
+        <v>1.4814</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3878</v>
+        <v>1.0467</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0203</v>
+        <v>0.4347</v>
       </c>
       <c r="V2" t="n">
         <v>0.3698</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.538</v>
+        <v>4.4321</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2085</v>
+        <v>-0.3144</v>
       </c>
       <c r="F3" t="n">
         <v>4.7466</v>
@@ -688,10 +688,10 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4711</v>
+        <v>0.423</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6609</v>
+        <v>0.2331</v>
       </c>
       <c r="U3" t="n">
         <v>0.1899</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9705</v>
+        <v>3.1603</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3394</v>
+        <v>0.5114</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3098</v>
+        <v>2.6489</v>
       </c>
       <c r="G4" t="n">
         <v>1.7618</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1595</v>
+        <v>0.0303</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5239</v>
+        <v>0.3269</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.2965</v>
       </c>
       <c r="V4" t="n">
         <v>1.1507</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6807</v>
+        <v>2.8534</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4604</v>
+        <v>-0.4726</v>
       </c>
       <c r="F5" t="n">
-        <v>3.141</v>
+        <v>3.326</v>
       </c>
       <c r="G5" t="n">
         <v>0.2283</v>
@@ -844,13 +844,13 @@
         <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5052</v>
+        <v>0.6675</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5924</v>
+        <v>0.3954</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0872</v>
+        <v>0.2722</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1085</v>
+        <v>1.2063</v>
       </c>
       <c r="E6" t="n">
-        <v>1.906</v>
+        <v>1.5667</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7975</v>
+        <v>-0.3604</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6557</v>
+        <v>-1.6734</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2222</v>
+        <v>-1.0853</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4335</v>
+        <v>-0.5881</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4091</v>
+        <v>-0.2405</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6752</v>
+        <v>-0.5864</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2661</v>
+        <v>0.3459</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0648</v>
+        <v>-1.4328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8974</v>
+        <v>-0.4989</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1674</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4814</v>
+        <v>0.1619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9542</v>
+        <v>0.1346</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4728</v>
+        <v>0.0273</v>
       </c>
       <c r="V6" t="n">
         <v>0.7602</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7602</v>
+        <v>1.8902</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.988</v>
+        <v>0.971</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8661</v>
+        <v>-0.7145</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8541</v>
+        <v>1.6854</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3456</v>
+        <v>2.6699</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2468</v>
+        <v>1.551</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0988</v>
+        <v>1.1188</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0398</v>
+        <v>3.3785</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1346</v>
+        <v>2.2843</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0948</v>
+        <v>1.0941</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3058</v>
+        <v>-0.7086</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1122</v>
+        <v>-0.7333</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1936</v>
+        <v>0.0247</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1751</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>-4.5676</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9474</v>
+        <v>0.2587</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4443</v>
+        <v>0.4747</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5031</v>
+        <v>-0.216</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2447</v>
+        <v>0.9401</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7592</v>
+        <v>1.5527</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5145</v>
+        <v>-0.6126</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6734</v>
+        <v>-1.6557</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0853</v>
+        <v>-0.2222</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5881</v>
+        <v>-1.4335</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2405</v>
+        <v>0.4091</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5864</v>
+        <v>0.6752</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3459</v>
+        <v>-0.2661</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4328</v>
+        <v>-2.0648</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4989</v>
+        <v>-0.8974</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9339</v>
+        <v>-1.1674</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7997</v>
+        <v>0.313</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.6009</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1268</v>
+        <v>-0.2878</v>
       </c>
       <c r="V8" t="n">
         <v>0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8902</v>
+        <v>0.7602</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0616</v>
+        <v>-1.2171</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1615</v>
+        <v>-2.3622</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2231</v>
+        <v>1.1451</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6699</v>
+        <v>1.3456</v>
       </c>
       <c r="H9" t="n">
-        <v>1.551</v>
+        <v>1.2468</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1188</v>
+        <v>0.0988</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3785</v>
+        <v>1.0398</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2843</v>
+        <v>1.1346</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0941</v>
+        <v>-0.0948</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7086</v>
+        <v>0.3058</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7333</v>
+        <v>0.1122</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0247</v>
+        <v>0.1936</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9576</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5676</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6506999999999999</v>
+        <v>0.7423</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0277</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6784</v>
+        <v>-0.2058</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0345</v>
+        <v>-3.6354</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1948</v>
+        <v>-1.6108</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8396</v>
+        <v>-2.0246</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7077</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0668</v>
+        <v>0.3323</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.548</v>
+        <v>0.0361</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4812</v>
+        <v>0.2962</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8417</v>
+        <v>-6.0409</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3607</v>
+        <v>-3.714</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.481</v>
+        <v>-2.3269</v>
       </c>
       <c r="G11" t="n">
         <v>-6.5582</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5414</v>
+        <v>0.3422</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8857</v>
+        <v>0.5324</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.395699999999998</v>
+        <v>10.4229</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.765899999999999</v>
+        <v>-2.7385</v>
       </c>
       <c r="F12" t="n">
-        <v>13.1616</v>
+        <v>13.1614</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4857</v>
@@ -1390,13 +1390,13 @@
         <v>22.8383</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7253</v>
+        <v>4.752599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7016</v>
+        <v>4.728899999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02379999999999993</v>
+        <v>0.02400000000000005</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5442999999999998</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0435</v>
+        <v>3.3134</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8886</v>
+        <v>1.7691</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1549</v>
+        <v>1.5444</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1878</v>
+        <v>1.0526</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9249</v>
+        <v>0.7785</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7371</v>
+        <v>0.2741</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7534999999999999</v>
+        <v>1.1118</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.83</v>
+        <v>0.8823</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4344</v>
+        <v>-0.0592</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.095</v>
+        <v>-0.1038</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6606</v>
+        <v>0.0446</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.305</v>
       </c>
       <c r="R13" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9714</v>
+        <v>-0.1439</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6872</v>
+        <v>0.0721</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2842</v>
+        <v>-0.216</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2599</v>
+        <v>1.5346</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2599</v>
+        <v>1.8902</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3555</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4244</v>
+        <v>3.0249</v>
       </c>
       <c r="E14" t="n">
-        <v>0.875</v>
+        <v>2.7679</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5495</v>
+        <v>0.257</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0526</v>
+        <v>5.1157</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7785</v>
+        <v>1.6909</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2741</v>
+        <v>3.4249</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1118</v>
+        <v>4.8769</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8823</v>
+        <v>2.3907</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2295</v>
+        <v>2.4862</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0592</v>
+        <v>0.2389</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1038</v>
+        <v>-0.6998</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0446</v>
+        <v>0.9387</v>
       </c>
       <c r="P14" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0329</v>
+        <v>0.1995</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.822</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2109</v>
+        <v>0.1334</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5346</v>
+        <v>-1.8553</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3555</v>
+        <v>-1.8553</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0821</v>
+        <v>1.9208</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0974</v>
+        <v>0.771</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0153</v>
+        <v>1.1498</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1157</v>
+        <v>-1.1878</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6909</v>
+        <v>-1.9249</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4249</v>
+        <v>0.7371</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8769</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3907</v>
+        <v>-0.83</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4862</v>
+        <v>0.0765</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2389</v>
+        <v>-0.4344</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6998</v>
+        <v>-1.095</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9387</v>
+        <v>0.6606</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.8487</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6044</v>
+        <v>0.5696</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1389</v>
+        <v>0.2791</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8553</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
+        <v>2.2599</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.8553</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0067</v>
+        <v>0.8358</v>
       </c>
       <c r="E16" t="n">
-        <v>0.531</v>
+        <v>-2.0001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4757</v>
+        <v>2.8359</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9713</v>
+        <v>1.9287</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4772</v>
+        <v>-0.0946</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4941</v>
+        <v>2.0232</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2129</v>
+        <v>0.4754</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9125</v>
+        <v>0.0912</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3005</v>
+        <v>0.3841</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2417</v>
+        <v>1.4533</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4353</v>
+        <v>-0.1858</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1936</v>
+        <v>1.6391</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4801</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0805</v>
+        <v>0.1772</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6682</v>
+        <v>-0.0829</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5876</v>
+        <v>0.2602</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0.0349</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3297</v>
+        <v>0.5224</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7766</v>
+        <v>-0.2513</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1064</v>
+        <v>0.7738</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9287</v>
+        <v>1.9713</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0946</v>
+        <v>0.4772</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0232</v>
+        <v>1.4941</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4754</v>
+        <v>2.2129</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0912</v>
+        <v>0.9125</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3841</v>
+        <v>1.3005</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4533</v>
+        <v>-0.2417</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1858</v>
+        <v>-0.4353</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6391</v>
+        <v>0.1936</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-3.4801</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3288</v>
+        <v>-0.4038</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1406</v>
+        <v>-0.1142</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4694</v>
+        <v>-0.2896</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0349</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.0349</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5004</v>
+        <v>-0.4079</v>
       </c>
       <c r="E18" t="n">
         <v>-1.1315</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6311</v>
+        <v>0.7236</v>
       </c>
       <c r="G18" t="n">
         <v>0.5711000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4539</v>
+        <v>-0.3614</v>
       </c>
       <c r="T18" t="n">
         <v>-0.137</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3169</v>
+        <v>-0.2244</v>
       </c>
       <c r="V18" t="n">
         <v>0.0349</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2274</v>
+        <v>-1.7916</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2426</v>
+        <v>-0.3273</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9848</v>
+        <v>-1.4643</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9193</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0707</v>
+        <v>1.031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1514</v>
+        <v>-0.5921</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4927</v>
+        <v>1.6567</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>1.8463</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1912</v>
+        <v>-0.1896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4266</v>
+        <v>-1.2178</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3867</v>
+        <v>-0.8153</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0399</v>
+        <v>-0.4024</v>
       </c>
       <c r="P19" t="n">
         <v>-1.0875</v>
@@ -1936,22 +1936,22 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9094</v>
+        <v>-0.578</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4252</v>
+        <v>0.1911</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5158</v>
+        <v>-0.7691</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4484</v>
+        <v>-2.4085</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6984</v>
+        <v>-4.5867</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2501</v>
+        <v>2.1782</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6916</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0312</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2704</v>
+        <v>-0.1586</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2617</v>
+        <v>0.1899</v>
       </c>
       <c r="V20" t="n">
         <v>0.7744</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5854</v>
+        <v>-3.1086</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9978</v>
+        <v>-2.3601</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5876</v>
+        <v>-0.7484</v>
       </c>
       <c r="G21" t="n">
-        <v>0.439</v>
+        <v>-0.9193</v>
       </c>
       <c r="H21" t="n">
-        <v>1.031</v>
+        <v>-1.0707</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5921</v>
+        <v>0.1514</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6567</v>
+        <v>-0.4927</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8463</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1896</v>
+        <v>0.1912</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2178</v>
+        <v>-0.4266</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8153</v>
+        <v>-0.3867</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4024</v>
+        <v>-0.0399</v>
       </c>
       <c r="P21" t="n">
         <v>-1.0875</v>
@@ -2092,22 +2092,22 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3719</v>
+        <v>0.0282</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4795</v>
+        <v>0.3076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8924</v>
+        <v>-0.2794</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9298</v>
+        <v>-3.5624</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2772</v>
+        <v>-3.0537</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6526</v>
+        <v>-0.5087</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5942</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7913</v>
+        <v>-0.4239</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4494</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1184</v>
+        <v>0.0255</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1093</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5907</v>
+        <v>-5.4989</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4292</v>
+        <v>-4.7586</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1615</v>
+        <v>-0.7402</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1998</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9559</v>
+        <v>-0.864</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9589</v>
+        <v>-0.2884</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9969</v>
+        <v>-0.5756</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.395700000000001</v>
+        <v>-7.160599999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-13.1613</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7659</v>
+        <v>6.0011</v>
       </c>
       <c r="G24" t="n">
         <v>2.4857</v>
@@ -2296,13 +2296,13 @@
         <v>-5.0647</v>
       </c>
       <c r="I24" t="n">
-        <v>7.550300000000001</v>
+        <v>7.550299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>4.399900000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2759000000000005</v>
+        <v>0.2758999999999996</v>
       </c>
       <c r="L24" t="n">
         <v>4.123900000000001</v>
@@ -2311,7 +2311,7 @@
         <v>-1.9144</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.340499999999999</v>
+        <v>-5.3405</v>
       </c>
       <c r="O24" t="n">
         <v>3.4262</v>
@@ -2326,16 +2326,16 @@
         <v>14.1378</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.725499999999999</v>
+        <v>-1.4902</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.02389999999999992</v>
+        <v>-0.02400000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.7013</v>
+        <v>-1.466</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5441000000000005</v>
+        <v>0.5441</v>
       </c>
       <c r="W24" t="n">
         <v>5.300800000000001</v>
